--- a/data/trans_orig/P34A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P34A_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2007</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2007 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80858</t>
+          <t>80469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110729</t>
+          <t>113151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71088</t>
+          <t>73045</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102769</t>
+          <t>103734</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>162846</t>
+          <t>161796</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207892</t>
+          <t>206376</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>158158</t>
+          <t>155736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>188029</t>
+          <t>188418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>156842</t>
+          <t>155877</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>188523</t>
+          <t>186566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>320605</t>
+          <t>322121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>365651</t>
+          <t>366701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138201</t>
+          <t>137704</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>182487</t>
+          <t>182123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>192163</t>
+          <t>194496</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>237617</t>
+          <t>237921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>347374</t>
+          <t>347124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>411898</t>
+          <t>406112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>308818</t>
+          <t>309182</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>353104</t>
+          <t>353601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>264289</t>
+          <t>263985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>309743</t>
+          <t>307410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>581312</t>
+          <t>587098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>645836</t>
+          <t>646086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116342</t>
+          <t>115604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152197</t>
+          <t>150088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118778</t>
+          <t>118449</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155155</t>
+          <t>154532</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243320</t>
+          <t>243488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293710</t>
+          <t>293883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165612</t>
+          <t>167721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201467</t>
+          <t>202205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180257</t>
+          <t>180880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216634</t>
+          <t>216963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>359511</t>
+          <t>359338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>409901</t>
+          <t>409733</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120614</t>
+          <t>120123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155590</t>
+          <t>157262</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135866</t>
+          <t>136573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171415</t>
+          <t>172487</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268075</t>
+          <t>267063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>317902</t>
+          <t>318862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>201555</t>
+          <t>199883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236531</t>
+          <t>237022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197155</t>
+          <t>196083</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>232704</t>
+          <t>231997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>407813</t>
+          <t>406853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>457640</t>
+          <t>458652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,2%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83626</t>
+          <t>82415</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109710</t>
+          <t>109148</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120510</t>
+          <t>121284</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148119</t>
+          <t>147715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212498</t>
+          <t>212455</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253594</t>
+          <t>250774</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84191</t>
+          <t>84753</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110275</t>
+          <t>111486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51634</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79243</t>
+          <t>78469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140060</t>
+          <t>142880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>181199</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84900</t>
+          <t>86440</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116631</t>
+          <t>116808</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107758</t>
+          <t>107281</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139732</t>
+          <t>140124</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>202246</t>
+          <t>201702</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>248223</t>
+          <t>249920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150134</t>
+          <t>149957</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181865</t>
+          <t>180325</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134489</t>
+          <t>134097</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166463</t>
+          <t>166940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>292763</t>
+          <t>291066</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>338740</t>
+          <t>339284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>246096</t>
+          <t>247033</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>296552</t>
+          <t>297179</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>266498</t>
+          <t>265236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>316393</t>
+          <t>312946</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>526955</t>
+          <t>525840</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>597002</t>
+          <t>595551</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>311330</t>
+          <t>310703</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>361786</t>
+          <t>360849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>309795</t>
+          <t>313242</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>359690</t>
+          <t>360952</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>637068</t>
+          <t>638519</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>707115</t>
+          <t>708230</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>303354</t>
+          <t>301489</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>354825</t>
+          <t>355778</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>360611</t>
+          <t>361013</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>418334</t>
+          <t>415097</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>680956</t>
+          <t>678280</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>758612</t>
+          <t>753809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>373044</t>
+          <t>372091</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>424515</t>
+          <t>426380</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>334765</t>
+          <t>338002</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>392488</t>
+          <t>392086</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>722356</t>
+          <t>727159</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>800012</t>
+          <t>802688</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1277681</t>
+          <t>1269057</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1387470</t>
+          <t>1384498</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1471330</t>
+          <t>1475908</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1592159</t>
+          <t>1591174</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2777688</t>
+          <t>2775725</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2943935</t>
+          <t>2940722</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1844093</t>
+          <t>1847065</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1953882</t>
+          <t>1962506</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1726600</t>
+          <t>1727585</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1847429</t>
+          <t>1842851</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3606387</t>
+          <t>3609600</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3772634</t>
+          <t>3774597</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2012</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58545</t>
+          <t>57069</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87848</t>
+          <t>90274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121306</t>
+          <t>122808</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154706</t>
+          <t>153348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199927</t>
+          <t>198657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>206890</t>
+          <t>204464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236193</t>
+          <t>237669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165939</t>
+          <t>164437</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199972</t>
+          <t>199951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>382056</t>
+          <t>383326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>427277</t>
+          <t>428635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90246</t>
+          <t>90679</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128116</t>
+          <t>129114</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161368</t>
+          <t>162279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206989</t>
+          <t>208315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>263854</t>
+          <t>263032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325599</t>
+          <t>322982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>377411</t>
+          <t>376413</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415281</t>
+          <t>414848</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316776</t>
+          <t>315450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362397</t>
+          <t>361486</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703693</t>
+          <t>706310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>765438</t>
+          <t>766260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47273</t>
+          <t>47364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76102</t>
+          <t>74684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52902</t>
+          <t>52535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81857</t>
+          <t>81426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106860</t>
+          <t>108439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147152</t>
+          <t>147844</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>247944</t>
+          <t>249362</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276773</t>
+          <t>276682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>259163</t>
+          <t>259594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288118</t>
+          <t>288485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517914</t>
+          <t>517222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>558206</t>
+          <t>556627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84750</t>
+          <t>88255</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>121674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111707</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148948</t>
+          <t>149905</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207141</t>
+          <t>208837</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>259753</t>
+          <t>261307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251521</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>288371</t>
+          <t>284866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>240003</t>
+          <t>239046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277244</t>
+          <t>276590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>502319</t>
+          <t>500765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>554931</t>
+          <t>553235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,6%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47012</t>
+          <t>47060</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74405</t>
+          <t>73305</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68151</t>
+          <t>69395</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98557</t>
+          <t>98944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124048</t>
+          <t>123822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163724</t>
+          <t>163163</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138213</t>
+          <t>139313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165606</t>
+          <t>165558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121034</t>
+          <t>120647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151440</t>
+          <t>150196</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268485</t>
+          <t>269046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308161</t>
+          <t>308387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,35%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28210</t>
+          <t>28407</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51127</t>
+          <t>52031</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>42158</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68269</t>
+          <t>68910</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75570</t>
+          <t>75701</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112058</t>
+          <t>111324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222854</t>
+          <t>221950</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245771</t>
+          <t>245574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211762</t>
+          <t>211121</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238377</t>
+          <t>237873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>441954</t>
+          <t>442688</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>478442</t>
+          <t>478311</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116647</t>
+          <t>114273</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159486</t>
+          <t>159114</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155748</t>
+          <t>155590</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>202006</t>
+          <t>202553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>281225</t>
+          <t>285646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>347858</t>
+          <t>347453</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>502405</t>
+          <t>502777</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>545244</t>
+          <t>547618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>490749</t>
+          <t>490202</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>537007</t>
+          <t>537165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1006788</t>
+          <t>1007193</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1073421</t>
+          <t>1069000</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>163252</t>
+          <t>165207</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>216292</t>
+          <t>215282</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>272960</t>
+          <t>269851</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>329826</t>
+          <t>328125</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>451464</t>
+          <t>452844</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>529149</t>
+          <t>532288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>562806</t>
+          <t>563816</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>615846</t>
+          <t>613891</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>494027</t>
+          <t>495728</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>550893</t>
+          <t>554002</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1073802</t>
+          <t>1070663</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1151487</t>
+          <t>1150107</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>720971</t>
+          <t>719512</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>825293</t>
+          <t>820113</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1042002</t>
+          <t>1045472</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1157285</t>
+          <t>1157918</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1796791</t>
+          <t>1793702</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1940903</t>
+          <t>1945254</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2599728</t>
+          <t>2604908</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2704050</t>
+          <t>2705509</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2399926</t>
+          <t>2399293</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2515209</t>
+          <t>2511739</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5041329</t>
+          <t>5036978</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5185441</t>
+          <t>5188530</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2016</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76225</t>
+          <t>78700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111928</t>
+          <t>112886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102618</t>
+          <t>102929</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136989</t>
+          <t>135882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189803</t>
+          <t>189554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237513</t>
+          <t>238872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>181833</t>
+          <t>180875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>217536</t>
+          <t>215061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151714</t>
+          <t>152821</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186085</t>
+          <t>185774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>344951</t>
+          <t>343592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>392661</t>
+          <t>392910</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129394</t>
+          <t>128826</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>170678</t>
+          <t>168520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>171166</t>
+          <t>171843</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>215553</t>
+          <t>216034</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>309654</t>
+          <t>311870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>371474</t>
+          <t>372982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331897</t>
+          <t>334055</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373181</t>
+          <t>373749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307531</t>
+          <t>307050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351918</t>
+          <t>351241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>654185</t>
+          <t>652677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>716005</t>
+          <t>713789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,59%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86664</t>
+          <t>84794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117348</t>
+          <t>118564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106494</t>
+          <t>106048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142348</t>
+          <t>142901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202458</t>
+          <t>203977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250353</t>
+          <t>251481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>201217</t>
+          <t>200001</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>231901</t>
+          <t>233771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193961</t>
+          <t>193408</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>229815</t>
+          <t>230261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>404521</t>
+          <t>403393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>452416</t>
+          <t>450897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65935</t>
+          <t>64747</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98205</t>
+          <t>97050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116475</t>
+          <t>117447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155524</t>
+          <t>155588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>188871</t>
+          <t>190106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242299</t>
+          <t>242317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271759</t>
+          <t>272914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>304029</t>
+          <t>305217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231759</t>
+          <t>231695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>270808</t>
+          <t>269836</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>514948</t>
+          <t>514930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>568376</t>
+          <t>567141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,9%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60701</t>
+          <t>60300</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86157</t>
+          <t>87590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91563</t>
+          <t>90763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118959</t>
+          <t>120598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160635</t>
+          <t>159410</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198800</t>
+          <t>198892</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125064</t>
+          <t>123631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150520</t>
+          <t>150921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99628</t>
+          <t>97989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127024</t>
+          <t>127824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>231008</t>
+          <t>230916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269173</t>
+          <t>270398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75645</t>
+          <t>75209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107439</t>
+          <t>106383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>98020</t>
+          <t>96818</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>130391</t>
+          <t>128977</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182274</t>
+          <t>181453</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>228824</t>
+          <t>226698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155684</t>
+          <t>156740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187478</t>
+          <t>187914</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>142724</t>
+          <t>144138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>175095</t>
+          <t>176297</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>307414</t>
+          <t>309540</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>353964</t>
+          <t>354785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>234166</t>
+          <t>234477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>286765</t>
+          <t>286599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>295678</t>
+          <t>291628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>345468</t>
+          <t>345005</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>547056</t>
+          <t>545028</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>621039</t>
+          <t>621408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,1%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>369793</t>
+          <t>369959</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>422392</t>
+          <t>422081</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>345826</t>
+          <t>346289</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395616</t>
+          <t>399666</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>726813</t>
+          <t>726444</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>800796</t>
+          <t>802824</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,56%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>271920</t>
+          <t>270456</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>324062</t>
+          <t>327109</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>373654</t>
+          <t>372789</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>431406</t>
+          <t>430031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>662538</t>
+          <t>659079</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>746043</t>
+          <t>742800</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>454521</t>
+          <t>451474</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>506663</t>
+          <t>508127</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>394761</t>
+          <t>396136</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>452513</t>
+          <t>453378</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>858707</t>
+          <t>861950</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>942212</t>
+          <t>945671</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1091965</t>
+          <t>1093989</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1204174</t>
+          <t>1211924</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1451762</t>
+          <t>1455725</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1571420</t>
+          <t>1574322</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2570329</t>
+          <t>2579108</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2735966</t>
+          <t>2745765</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2190176</t>
+          <t>2182426</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2302385</t>
+          <t>2300361</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1973122</t>
+          <t>1970220</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2092780</t>
+          <t>2088817</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4202926</t>
+          <t>4193127</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4368563</t>
+          <t>4359784</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre en 2023</t>
+          <t>Población que no realiza actividad física en su tiempo libre en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112646</t>
+          <t>109919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>152665</t>
+          <t>151776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130768</t>
+          <t>131230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>160096</t>
+          <t>160070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>251163</t>
+          <t>252159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>301701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>158778</t>
+          <t>159667</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>198797</t>
+          <t>201524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129539</t>
+          <t>129565</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158867</t>
+          <t>158405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>297485</t>
+          <t>299376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>349914</t>
+          <t>348918</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,05%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>169433</t>
+          <t>168284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>228525</t>
+          <t>223453</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>248328</t>
+          <t>251433</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>291338</t>
+          <t>290495</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>432425</t>
+          <t>430766</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>503308</t>
+          <t>504995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>288369</t>
+          <t>293441</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>347461</t>
+          <t>348610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223052</t>
+          <t>223895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>266062</t>
+          <t>262957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>527976</t>
+          <t>526289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>598859</t>
+          <t>600518</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,23%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100059</t>
+          <t>100318</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133705</t>
+          <t>134563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123633</t>
+          <t>122011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154224</t>
+          <t>152853</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231570</t>
+          <t>230198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275947</t>
+          <t>275305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>182345</t>
+          <t>181487</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215991</t>
+          <t>215732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>194904</t>
+          <t>196275</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>225495</t>
+          <t>227117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>389231</t>
+          <t>389873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>433608</t>
+          <t>434980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88056</t>
+          <t>87624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130870</t>
+          <t>131895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112523</t>
+          <t>111954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>237752</t>
+          <t>236215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>215919</t>
+          <t>221932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>351842</t>
+          <t>349251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181096</t>
+          <t>180071</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>223910</t>
+          <t>224342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>237966</t>
+          <t>239503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363195</t>
+          <t>363764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>435842</t>
+          <t>438433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>571765</t>
+          <t>565752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>22790</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35872</t>
+          <t>35392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37209</t>
+          <t>37955</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55482</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153806</t>
+          <t>154315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166335</t>
+          <t>166582</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172025</t>
+          <t>172505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186123</t>
+          <t>185107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>331157</t>
+          <t>330779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>349430</t>
+          <t>348684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94377</t>
+          <t>95541</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123657</t>
+          <t>124749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>97178</t>
+          <t>96804</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>120997</t>
+          <t>122101</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>200192</t>
+          <t>197574</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239257</t>
+          <t>238412</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145979</t>
+          <t>144887</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>174095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136059</t>
+          <t>134955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159878</t>
+          <t>160252</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>287435</t>
+          <t>288280</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>326500</t>
+          <t>329118</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>152010</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200488</t>
+          <t>201159</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126948</t>
+          <t>128951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>355535</t>
+          <t>355083</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>271954</t>
+          <t>263510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>520228</t>
+          <t>520330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>418834</t>
+          <t>418163</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>469365</t>
+          <t>467312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>489855</t>
+          <t>490307</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>718442</t>
+          <t>716439</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>944484</t>
+          <t>944382</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1192758</t>
+          <t>1201202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96993</t>
+          <t>99055</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>298523</t>
+          <t>296534</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>233616</t>
+          <t>234417</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>277002</t>
+          <t>276976</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>276330</t>
+          <t>281609</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>558288</t>
+          <t>560945</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>627970</t>
+          <t>629959</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>829500</t>
+          <t>827438</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>437034</t>
+          <t>437060</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>480420</t>
+          <t>479619</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1082241</t>
+          <t>1079584</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1364199</t>
+          <t>1358920</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>804984</t>
+          <t>822048</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1168999</t>
+          <t>1173211</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1129133</t>
+          <t>1124899</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1500600</t>
+          <t>1504516</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2136716</t>
+          <t>2135725</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2634551</t>
+          <t>2627855</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2281547</t>
+          <t>2277335</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2645562</t>
+          <t>2628498</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2152648</t>
+          <t>2148732</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2524115</t>
+          <t>2528349</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4469243</t>
+          <t>4475939</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4967078</t>
+          <t>4968069</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P34A_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80469</t>
+          <t>81202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113151</t>
+          <t>112339</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73045</t>
+          <t>71687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103734</t>
+          <t>103757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161796</t>
+          <t>163531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206376</t>
+          <t>207085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155736</t>
+          <t>156548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>188418</t>
+          <t>187685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155877</t>
+          <t>155854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186566</t>
+          <t>187924</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>322121</t>
+          <t>321412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>366701</t>
+          <t>364966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>137704</t>
+          <t>139927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>182123</t>
+          <t>182159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194496</t>
+          <t>193500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>237921</t>
+          <t>239300</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>347124</t>
+          <t>349079</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>406112</t>
+          <t>408339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>309182</t>
+          <t>309146</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>353601</t>
+          <t>351378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263985</t>
+          <t>262606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>307410</t>
+          <t>308406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>587098</t>
+          <t>584871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>646086</t>
+          <t>644131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115604</t>
+          <t>114071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150088</t>
+          <t>150216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118449</t>
+          <t>117670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154532</t>
+          <t>151769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243488</t>
+          <t>243113</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293883</t>
+          <t>293135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167721</t>
+          <t>167593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202205</t>
+          <t>203738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180880</t>
+          <t>183643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216963</t>
+          <t>217742</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>359338</t>
+          <t>360086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>409733</t>
+          <t>410108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120123</t>
+          <t>120321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157262</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136573</t>
+          <t>135528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172487</t>
+          <t>172950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>267063</t>
+          <t>264923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>318862</t>
+          <t>318380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199883</t>
+          <t>200784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237022</t>
+          <t>236824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196083</t>
+          <t>195620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>231997</t>
+          <t>233042</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>406853</t>
+          <t>407335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>458652</t>
+          <t>460792</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82415</t>
+          <t>81671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109148</t>
+          <t>110412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121284</t>
+          <t>121638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147715</t>
+          <t>150230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212455</t>
+          <t>211713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>250774</t>
+          <t>251267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84753</t>
+          <t>83489</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111486</t>
+          <t>112230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52038</t>
+          <t>49523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78469</t>
+          <t>78115</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142880</t>
+          <t>142387</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181199</t>
+          <t>181941</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86440</t>
+          <t>85961</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116808</t>
+          <t>117510</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107281</t>
+          <t>106092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>140124</t>
+          <t>138996</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>201702</t>
+          <t>200398</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>249920</t>
+          <t>246086</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>149255</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180325</t>
+          <t>180804</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134097</t>
+          <t>135225</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166940</t>
+          <t>168129</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>291066</t>
+          <t>294900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>339284</t>
+          <t>340588</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>247033</t>
+          <t>248257</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>297179</t>
+          <t>298360</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>265236</t>
+          <t>263486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>312946</t>
+          <t>312777</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>525840</t>
+          <t>528802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>595551</t>
+          <t>596617</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>310703</t>
+          <t>309522</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>360849</t>
+          <t>359625</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>313242</t>
+          <t>313411</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>360952</t>
+          <t>362702</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>638519</t>
+          <t>637453</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>708230</t>
+          <t>705268</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,15%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>301489</t>
+          <t>302495</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>355778</t>
+          <t>356858</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>361013</t>
+          <t>359253</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>415097</t>
+          <t>417985</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>678280</t>
+          <t>679848</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>753809</t>
+          <t>756046</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>372091</t>
+          <t>371011</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>426380</t>
+          <t>425374</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>338002</t>
+          <t>335114</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>392086</t>
+          <t>393846</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>727159</t>
+          <t>724922</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>802688</t>
+          <t>801120</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1269057</t>
+          <t>1266243</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1384498</t>
+          <t>1378935</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1475908</t>
+          <t>1472231</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1591174</t>
+          <t>1591192</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2775725</t>
+          <t>2778487</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2940722</t>
+          <t>2944256</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1847065</t>
+          <t>1852628</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1962506</t>
+          <t>1965320</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1727585</t>
+          <t>1727567</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1842851</t>
+          <t>1846528</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3609600</t>
+          <t>3606066</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3774597</t>
+          <t>3771835</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>59423</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90274</t>
+          <t>88789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>88352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122808</t>
+          <t>122558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153348</t>
+          <t>152586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198657</t>
+          <t>199268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>204464</t>
+          <t>205949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237669</t>
+          <t>235315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164437</t>
+          <t>164687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199951</t>
+          <t>198893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>383326</t>
+          <t>382715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>428635</t>
+          <t>429397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,78%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90679</t>
+          <t>90496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129114</t>
+          <t>127764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162279</t>
+          <t>160890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>208315</t>
+          <t>206480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>263032</t>
+          <t>267687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322982</t>
+          <t>324616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376413</t>
+          <t>377763</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414848</t>
+          <t>415031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315450</t>
+          <t>317285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361486</t>
+          <t>362875</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>706310</t>
+          <t>704676</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>766260</t>
+          <t>761605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>48514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74684</t>
+          <t>74816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>52041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81426</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108439</t>
+          <t>105871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147844</t>
+          <t>148423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249362</t>
+          <t>249230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276682</t>
+          <t>275532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>259594</t>
+          <t>259616</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288485</t>
+          <t>288979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517222</t>
+          <t>516643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>556627</t>
+          <t>559195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88255</t>
+          <t>85491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121674</t>
+          <t>122509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112361</t>
+          <t>109938</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149905</t>
+          <t>148570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>208837</t>
+          <t>209204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261307</t>
+          <t>261802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251447</t>
+          <t>250612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>284866</t>
+          <t>287630</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239046</t>
+          <t>240381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>276590</t>
+          <t>279013</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>500765</t>
+          <t>500270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>553235</t>
+          <t>552868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,55%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47060</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73305</t>
+          <t>74578</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69395</t>
+          <t>69436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98944</t>
+          <t>97707</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123822</t>
+          <t>123909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163163</t>
+          <t>164888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139313</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165558</t>
+          <t>165792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120647</t>
+          <t>121884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>150196</t>
+          <t>150155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>269046</t>
+          <t>267321</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308387</t>
+          <t>308300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28407</t>
+          <t>28406</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52031</t>
+          <t>52504</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42158</t>
+          <t>41718</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68910</t>
+          <t>68235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75701</t>
+          <t>75925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111324</t>
+          <t>110692</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221950</t>
+          <t>221477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245574</t>
+          <t>245575</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211121</t>
+          <t>211796</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237873</t>
+          <t>238313</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>442688</t>
+          <t>443320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>478311</t>
+          <t>478087</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114273</t>
+          <t>117386</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159114</t>
+          <t>160621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155590</t>
+          <t>156092</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>202553</t>
+          <t>204473</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>285646</t>
+          <t>279663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>347453</t>
+          <t>346016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>502777</t>
+          <t>501270</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>547618</t>
+          <t>544505</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>490202</t>
+          <t>488282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>537165</t>
+          <t>536663</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1007193</t>
+          <t>1008630</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1069000</t>
+          <t>1074983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>165207</t>
+          <t>164509</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>215282</t>
+          <t>214983</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>269851</t>
+          <t>273455</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>328125</t>
+          <t>330551</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>452844</t>
+          <t>451562</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>532288</t>
+          <t>531225</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>563816</t>
+          <t>564115</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>613891</t>
+          <t>614589</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>495728</t>
+          <t>493302</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>554002</t>
+          <t>550398</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1070663</t>
+          <t>1071726</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1150107</t>
+          <t>1151389</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>719512</t>
+          <t>719529</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>820113</t>
+          <t>818528</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1045472</t>
+          <t>1041111</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1157918</t>
+          <t>1153592</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1793702</t>
+          <t>1797037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1945254</t>
+          <t>1943348</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2604908</t>
+          <t>2606493</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2705509</t>
+          <t>2705492</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2399293</t>
+          <t>2403619</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2511739</t>
+          <t>2516100</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5036978</t>
+          <t>5038884</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5188530</t>
+          <t>5185195</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78700</t>
+          <t>77613</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112886</t>
+          <t>112658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102929</t>
+          <t>101389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135882</t>
+          <t>136180</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189554</t>
+          <t>189417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>238872</t>
+          <t>236573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>180875</t>
+          <t>181103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215061</t>
+          <t>216148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152821</t>
+          <t>152523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185774</t>
+          <t>187314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343592</t>
+          <t>345891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>392910</t>
+          <t>393047</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128826</t>
+          <t>129047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168520</t>
+          <t>170955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>171843</t>
+          <t>171952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>216034</t>
+          <t>217885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>311870</t>
+          <t>312650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>372982</t>
+          <t>374122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>334055</t>
+          <t>331620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373749</t>
+          <t>373528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307050</t>
+          <t>305199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351241</t>
+          <t>351132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>652677</t>
+          <t>651537</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713789</t>
+          <t>713009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84794</t>
+          <t>86353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118564</t>
+          <t>118428</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106048</t>
+          <t>107056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142901</t>
+          <t>141682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203977</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>251481</t>
+          <t>250703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200001</t>
+          <t>200137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>233771</t>
+          <t>232212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193408</t>
+          <t>194627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>230261</t>
+          <t>229253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>403393</t>
+          <t>404171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>450897</t>
+          <t>453035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64747</t>
+          <t>64597</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97050</t>
+          <t>96636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117447</t>
+          <t>114965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155588</t>
+          <t>154139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190106</t>
+          <t>188849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242317</t>
+          <t>241684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>272914</t>
+          <t>273328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>305217</t>
+          <t>305367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231695</t>
+          <t>233144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>269836</t>
+          <t>272318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>514930</t>
+          <t>515563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>567141</t>
+          <t>568398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60300</t>
+          <t>60782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87590</t>
+          <t>88040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90763</t>
+          <t>90413</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120598</t>
+          <t>120217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>159410</t>
+          <t>160486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198892</t>
+          <t>200392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123631</t>
+          <t>123181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150921</t>
+          <t>150439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97989</t>
+          <t>98370</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127824</t>
+          <t>128174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>229416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>270398</t>
+          <t>269322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75209</t>
+          <t>77732</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106383</t>
+          <t>106755</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96818</t>
+          <t>98459</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>128977</t>
+          <t>129823</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>181453</t>
+          <t>182006</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>226698</t>
+          <t>227413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,41%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156740</t>
+          <t>156368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187914</t>
+          <t>185391</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144138</t>
+          <t>143292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>176297</t>
+          <t>174656</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>309540</t>
+          <t>308825</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>354785</t>
+          <t>354232</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>234477</t>
+          <t>235452</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>286599</t>
+          <t>287437</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>291628</t>
+          <t>293633</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>345005</t>
+          <t>345863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>545028</t>
+          <t>548989</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>621408</t>
+          <t>626060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>369959</t>
+          <t>369121</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>422081</t>
+          <t>421106</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>346289</t>
+          <t>345431</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>399666</t>
+          <t>397661</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>726444</t>
+          <t>721792</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>802824</t>
+          <t>798863</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,27%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>270456</t>
+          <t>272293</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>327109</t>
+          <t>323189</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>372789</t>
+          <t>371064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>430031</t>
+          <t>431806</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>659079</t>
+          <t>658600</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>742800</t>
+          <t>741822</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>451474</t>
+          <t>455394</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>508127</t>
+          <t>506290</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>396136</t>
+          <t>394361</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>453378</t>
+          <t>455103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>861950</t>
+          <t>862928</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>945671</t>
+          <t>946150</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1093989</t>
+          <t>1092772</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1211924</t>
+          <t>1209112</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1455725</t>
+          <t>1458520</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1574322</t>
+          <t>1578005</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2579108</t>
+          <t>2589110</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2745765</t>
+          <t>2748514</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2182426</t>
+          <t>2185238</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2300361</t>
+          <t>2301578</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1970220</t>
+          <t>1966537</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2088817</t>
+          <t>2086022</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4193127</t>
+          <t>4190378</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4359784</t>
+          <t>4349782</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>131640</t>
+          <t>143732</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109919</t>
+          <t>125766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151776</t>
+          <t>159708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>145597</t>
+          <t>160526</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131230</t>
+          <t>144103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>160070</t>
+          <t>174222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>277237</t>
+          <t>304257</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252159</t>
+          <t>281546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>301701</t>
+          <t>327313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>179803</t>
+          <t>175113</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159667</t>
+          <t>159137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201524</t>
+          <t>193079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>144038</t>
+          <t>155535</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129565</t>
+          <t>141839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158405</t>
+          <t>171958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>323840</t>
+          <t>330649</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>299376</t>
+          <t>307593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>348918</t>
+          <t>353360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>55,66%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>196051</t>
+          <t>206915</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168284</t>
+          <t>179472</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223453</t>
+          <t>233545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>271267</t>
+          <t>290093</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>251433</t>
+          <t>268286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>290495</t>
+          <t>310614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>467318</t>
+          <t>497008</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>430766</t>
+          <t>463395</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>504995</t>
+          <t>534451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>320843</t>
+          <t>322308</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293441</t>
+          <t>295678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348610</t>
+          <t>349751</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>243123</t>
+          <t>255803</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223895</t>
+          <t>235282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>262957</t>
+          <t>277610</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>563966</t>
+          <t>578111</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>526289</t>
+          <t>540668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>600518</t>
+          <t>611724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516894</t>
+          <t>529223</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516894</t>
+          <t>529223</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516894</t>
+          <t>529223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514390</t>
+          <t>545896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514390</t>
+          <t>545896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514390</t>
+          <t>545896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031284</t>
+          <t>1075119</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031284</t>
+          <t>1075119</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031284</t>
+          <t>1075119</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>116156</t>
+          <t>117313</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100318</t>
+          <t>101490</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134563</t>
+          <t>135227</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>137850</t>
+          <t>142623</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122011</t>
+          <t>127439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152853</t>
+          <t>158654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>254006</t>
+          <t>259937</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>230198</t>
+          <t>238609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275305</t>
+          <t>282502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>199894</t>
+          <t>198680</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181487</t>
+          <t>180766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215732</t>
+          <t>214503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>211278</t>
+          <t>213758</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>196275</t>
+          <t>197727</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>227117</t>
+          <t>228942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>411172</t>
+          <t>412438</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -11576,22 +11576,22 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>434980</t>
+          <t>433766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>64,51%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>108087</t>
+          <t>128279</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87624</t>
+          <t>102594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131895</t>
+          <t>151281</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>178372</t>
+          <t>164064</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>145168</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236215</t>
+          <t>184539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>286458</t>
+          <t>292343</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221932</t>
+          <t>264857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>349251</t>
+          <t>326774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>203879</t>
+          <t>244209</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180071</t>
+          <t>221207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224342</t>
+          <t>269894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>297346</t>
+          <t>257897</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239503</t>
+          <t>237422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363764</t>
+          <t>276793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>501226</t>
+          <t>502107</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438433</t>
+          <t>467676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>565752</t>
+          <t>529593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311966</t>
+          <t>372488</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311966</t>
+          <t>372488</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311966</t>
+          <t>372488</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787684</t>
+          <t>794450</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787684</t>
+          <t>794450</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787684</t>
+          <t>794450</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>13213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>27015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22790</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35392</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>46084</t>
+          <t>49767</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37955</t>
+          <t>42045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55860</t>
+          <t>61575</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>161134</t>
+          <t>186799</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154315</t>
+          <t>178650</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166582</t>
+          <t>192452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>179421</t>
+          <t>195535</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172505</t>
+          <t>187966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185107</t>
+          <t>202331</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>340555</t>
+          <t>382333</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>330779</t>
+          <t>370525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>348684</t>
+          <t>390055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207897</t>
+          <t>226436</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207897</t>
+          <t>226436</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207897</t>
+          <t>226436</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386639</t>
+          <t>432100</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386639</t>
+          <t>432100</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386639</t>
+          <t>432100</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>108991</t>
+          <t>114766</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95541</t>
+          <t>100797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124749</t>
+          <t>129815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>108977</t>
+          <t>113029</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96804</t>
+          <t>98554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122101</t>
+          <t>125331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>217968</t>
+          <t>227795</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>197574</t>
+          <t>207825</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>238412</t>
+          <t>247378</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>160645</t>
+          <t>155941</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>144887</t>
+          <t>140892</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>174095</t>
+          <t>169910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>148079</t>
+          <t>150721</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134955</t>
+          <t>138419</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>160252</t>
+          <t>165196</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>308724</t>
+          <t>306662</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>288280</t>
+          <t>287079</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>329118</t>
+          <t>326632</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>61,11%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>207487</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152010</t>
+          <t>177807</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201159</t>
+          <t>233181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>261424</t>
+          <t>314867</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>128951</t>
+          <t>287534</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>355083</t>
+          <t>340116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>435910</t>
+          <t>522354</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>263510</t>
+          <t>483838</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>520330</t>
+          <t>561057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>444836</t>
+          <t>506758</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>418163</t>
+          <t>481064</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>467312</t>
+          <t>536438</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>583966</t>
+          <t>451584</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>490307</t>
+          <t>426335</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>716439</t>
+          <t>478917</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1028802</t>
+          <t>958343</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>944382</t>
+          <t>919640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1201202</t>
+          <t>996859</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>619322</t>
+          <t>714245</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>619322</t>
+          <t>714245</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>619322</t>
+          <t>714245</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>845390</t>
+          <t>766451</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>845390</t>
+          <t>766451</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>845390</t>
+          <t>766451</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1464712</t>
+          <t>1480697</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1464712</t>
+          <t>1480697</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1464712</t>
+          <t>1480697</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>213083</t>
+          <t>240946</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99055</t>
+          <t>214170</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>296534</t>
+          <t>268830</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>255049</t>
+          <t>292727</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>234417</t>
+          <t>268742</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>276976</t>
+          <t>316595</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>468132</t>
+          <t>533674</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>281609</t>
+          <t>495296</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>560945</t>
+          <t>567450</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>713410</t>
+          <t>554681</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>629959</t>
+          <t>526797</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>827438</t>
+          <t>581457</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>458987</t>
+          <t>536368</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>437060</t>
+          <t>512500</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>479619</t>
+          <t>560353</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1172397</t>
+          <t>1091048</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1079584</t>
+          <t>1057272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1358920</t>
+          <t>1129426</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926493</t>
+          <t>795627</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926493</t>
+          <t>795627</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926493</t>
+          <t>795627</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714036</t>
+          <t>829095</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714036</t>
+          <t>829095</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714036</t>
+          <t>829095</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1640529</t>
+          <t>1624722</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1640529</t>
+          <t>1624722</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1640529</t>
+          <t>1624722</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1066102</t>
+          <t>1178305</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>822048</t>
+          <t>1117217</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1173211</t>
+          <t>1240274</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1387012</t>
+          <t>1508830</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1124899</t>
+          <t>1458472</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1504516</t>
+          <t>1558289</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2453114</t>
+          <t>2687135</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2135725</t>
+          <t>2610556</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2627855</t>
+          <t>2762835</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2384444</t>
+          <t>2344489</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2277335</t>
+          <t>2282520</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2628498</t>
+          <t>2405577</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2266236</t>
+          <t>2217201</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2148732</t>
+          <t>2167742</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2528349</t>
+          <t>2267559</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4650680</t>
+          <t>4561690</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4475939</t>
+          <t>4485990</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4968069</t>
+          <t>4638269</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
